--- a/backtest_runs/20260410_193731/by_symbol/LSECL/LSECL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/LSECL/LSECL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-1335.880000000005</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>101908.4</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>101908.4</v>
@@ -771,7 +771,7 @@
         <v>-954.1999999999966</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>110114.52</v>
@@ -817,7 +817,7 @@
         <v>-763.3600000000007</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>109351.16</v>
@@ -863,7 +863,7 @@
         <v>-572.5199999999878</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>108778.64</v>
@@ -909,7 +909,7 @@
         <v>-4961.840000000013</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>103816.8</v>
@@ -1001,7 +1001,7 @@
         <v>-381.6799999999919</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>104771</v>
@@ -1185,7 +1185,7 @@
         <v>-6297.720000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>106106.88</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>106870.24</v>
@@ -1415,7 +1415,7 @@
         <v>-1717.559999999997</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>108778.64</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>109732.84</v>
@@ -1553,7 +1553,7 @@
         <v>-381.6799999999919</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>109351.16</v>
@@ -1645,7 +1645,7 @@
         <v>-3816.800000000003</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>112595.44</v>
